--- a/data/biomass/BourgneufBay_DryWeight_Cores.xlsx
+++ b/data/biomass/BourgneufBay_DryWeight_Cores.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Documents\GiHub\Fieldtrip_Rewrite_Sept2025\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REWRITE\Field_data\seagrass_carbon_2025\data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54668F53-789C-4509-9732-6B9A4E1D0A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D0DD0061-F6DC-423E-8A37-C6F61312652F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20550" windowHeight="9525"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -230,8 +229,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,11 +600,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A924C369-EB97-4A90-9A43-7BBAE1C2FC37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -627,7 +626,7 @@
         <v>1.256</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -638,7 +637,7 @@
         <v>0.63600000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -649,7 +648,7 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -660,7 +659,7 @@
         <v>1.121</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -671,7 +670,7 @@
         <v>1.6659999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -682,7 +681,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -693,7 +692,7 @@
         <v>0.32200000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -704,7 +703,7 @@
         <v>0.91300000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -715,7 +714,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -726,7 +725,7 @@
         <v>0.71699999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -737,7 +736,7 @@
         <v>1.169</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -748,7 +747,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -759,7 +758,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -770,7 +769,7 @@
         <v>1.0680000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -778,7 +777,7 @@
         <v>0.628</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -789,7 +788,7 @@
         <v>0.60899999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -800,7 +799,7 @@
         <v>0.77400000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -811,7 +810,7 @@
         <v>1.2589999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -822,7 +821,7 @@
         <v>0.309</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -833,7 +832,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -844,7 +843,7 @@
         <v>1.0960000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -855,7 +854,7 @@
         <v>0.51200000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -866,7 +865,7 @@
         <v>0.54700000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -877,7 +876,7 @@
         <v>0.32600000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -888,12 +887,12 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -904,7 +903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -915,7 +914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -926,7 +925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -937,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -948,7 +947,7 @@
         <v>0.91600000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -959,18 +958,19 @@
         <v>1.845</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34">
-        <v>1.921</v>
+        <f>1.86-0.004-0.0096</f>
+        <v>1.8464</v>
       </c>
       <c r="C34">
         <v>1.748</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -981,7 +981,7 @@
         <v>0.32100000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -989,10 +989,11 @@
         <v>0.91600000000000004</v>
       </c>
       <c r="C36">
-        <v>1.369</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+        <f>1.369-0.0038</f>
+        <v>1.3652</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1003,7 +1004,7 @@
         <v>1.4570000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1014,7 +1015,7 @@
         <v>0.98699999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1025,7 +1026,7 @@
         <v>1.339</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1036,7 +1037,7 @@
         <v>0.76200000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1047,18 +1048,19 @@
         <v>0.626</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>43</v>
       </c>
       <c r="B42">
-        <v>0.80400000000000005</v>
+        <f>0.804-0.001</f>
+        <v>0.80300000000000005</v>
       </c>
       <c r="C42">
         <v>0.53700000000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1066,32 +1068,37 @@
         <v>0.86299999999999999</v>
       </c>
       <c r="C43">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+        <f>0.97-0.02</f>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>45</v>
       </c>
       <c r="B44">
-        <v>1.411</v>
+        <f>1.411-0.026</f>
+        <v>1.385</v>
       </c>
       <c r="C44">
-        <v>1.7809999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+        <f>1.781-0.078</f>
+        <v>1.7029999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
       <c r="B45">
-        <v>1.845</v>
+        <f>1.845-0.004</f>
+        <v>1.841</v>
       </c>
       <c r="C45">
-        <v>0.93700000000000006</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+        <f>0.937-0.015</f>
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1102,7 +1109,7 @@
         <v>0.20200000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1113,7 +1120,7 @@
         <v>1.079</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1124,7 +1131,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1135,7 +1142,7 @@
         <v>0.54900000000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -1146,18 +1153,20 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
       <c r="B51">
-        <v>2.3719999999999999</v>
+        <f>2.372-0.058</f>
+        <v>2.3140000000000001</v>
       </c>
       <c r="C51">
-        <v>1.629</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+        <f>1.629-0.048-0.011-0.004</f>
+        <v>1.5660000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -1168,7 +1177,7 @@
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -1179,7 +1188,7 @@
         <v>0.42099999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -1187,10 +1196,11 @@
         <v>0.76600000000000001</v>
       </c>
       <c r="C54">
-        <v>0.29399999999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+        <f>0.294-0.006</f>
+        <v>0.28799999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1201,7 +1211,7 @@
         <v>0.38200000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -1212,7 +1222,7 @@
         <v>1.1819999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1223,7 +1233,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -1234,7 +1244,7 @@
         <v>0.93400000000000005</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -1245,7 +1255,7 @@
         <v>0.78700000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -1256,7 +1266,7 @@
         <v>0.627</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1264,7 +1274,8 @@
         <v>1.2170000000000001</v>
       </c>
       <c r="C61">
-        <v>0.95099999999999996</v>
+        <f>0.951-0.0124</f>
+        <v>0.93859999999999999</v>
       </c>
     </row>
   </sheetData>
